--- a/Docs/Update Required By sayan.xlsx
+++ b/Docs/Update Required By sayan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\All Projects(personal and office)\DZ2CLOUD PROJECTS\Arogya Diagonistics website\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EAFA8C-E1CC-4664-B453-CCF83CBAA541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0259B3DF-F1A4-4300-8640-B0772672D067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
     <t>task</t>
   </si>
@@ -40,6 +40,12 @@
   </si>
   <si>
     <t>all input fiend validation (formate, size, type)</t>
+  </si>
+  <si>
+    <t>email from supabase</t>
+  </si>
+  <si>
+    <t>Booking should be two tab test booking and doctor booking</t>
   </si>
 </sst>
 </file>
@@ -364,10 +370,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D2:E4"/>
+  <dimension ref="D2:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="44.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="4:5" x14ac:dyDescent="0.25">
@@ -394,6 +400,22 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
